--- a/data/LINE班群提醒排程.xlsx
+++ b/data/LINE班群提醒排程.xlsx
@@ -1,41 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F101660\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sonialiang/Desktop/兆基/LINE班群提醒排程/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7784BA8-46F1-4A51-A066-0E100EB1F82A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42162641-B2F6-7547-815C-43B388D9C8E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3780" yWindow="600" windowWidth="21820" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="提醒排程" sheetId="1" r:id="rId1"/>
     <sheet name="班群設定" sheetId="2" r:id="rId2"/>
     <sheet name="使用說明" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="63">
   <si>
     <t>提醒類別</t>
   </si>
@@ -236,34 +223,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> Ua04bea4032a64049a9eabc6fe46b52c5</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>81242b20-e254-4db3-9dc1-17e93fd25a4d</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>674a2602-26c2-43f5-b17a-a690285ab2cf</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>期末考試</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>企業個案分析</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>考試提醒</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>2006/5/4</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve"> • 5/7 </t>
     </r>
@@ -274,58 +233,7 @@
         <family val="2"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">報告組別：第 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>②</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> 組 → 第 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>③</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> 組 → 第 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>⑤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> 組
+      <t>報告組別：第 ② 組 → 第 ③ 組 → 第 ⑤ 組
     ：今天要帶</t>
     </r>
     <r>
@@ -371,58 +279,7 @@
         <family val="2"/>
         <charset val="136"/>
       </rPr>
-      <t xml:space="preserve">報告組別：第 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>①</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> 組 → 第 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>⑥</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> 組 → 第 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>④</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> 組
+      <t>報告組別：第 ① 組 → 第 ⑥ 組 → 第 ④ 組
     請於今天繳交</t>
     </r>
     <r>
@@ -498,17 +355,27 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve"> • </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>大家地得帶學生證</t>
-    </r>
+    <t xml:space="preserve"> Ua04bea4032a64049a9eabc6fe46b52c5</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>81242b20-e254-4db3-9dc1-17e93fd25a4d</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>674a2602-26c2-43f5-b17a-a690285ab2cf</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>期末考試</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>企業個案分析</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>考試提醒</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -516,7 +383,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -580,11 +447,6 @@
     <font>
       <sz val="10"/>
       <name val="Microsoft JhengHei"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Segoe UI Symbol"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -653,7 +515,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -691,6 +553,9 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -700,22 +565,12 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1019,12 +874,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="35.19921875" customWidth="1"/>
-    <col min="4" max="4" width="13" style="21" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="44" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
@@ -1042,7 +897,7 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -1071,7 +926,7 @@
       <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
@@ -1098,9 +953,9 @@
         <v>53</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E3" s="4" t="s">
@@ -1121,44 +976,42 @@
       <c r="A4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>60</v>
+      <c r="B4" s="16" t="s">
+        <v>61</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="13">
+        <v>46146</v>
+      </c>
+      <c r="E4" s="14" t="s">
         <v>55</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="G4" s="8"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
     </row>
     <row r="5" spans="1:9" ht="49" customHeight="1">
-      <c r="A5" s="14" t="s">
-        <v>59</v>
+      <c r="A5" s="15" t="s">
+        <v>60</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>53</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D5" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="17">
+        <v>46188</v>
+      </c>
+      <c r="E5" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>64</v>
-      </c>
+      <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="5"/>
       <c r="I5" s="6"/>
@@ -1172,7 +1025,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
@@ -1221,7 +1074,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="70" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>

--- a/data/LINE班群提醒排程.xlsx
+++ b/data/LINE班群提醒排程.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sonialiang/Desktop/兆基/LINE班群提醒排程/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sonialiang/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{488EE8EA-BAAC-8B47-A91E-A94F5015DB82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A75EA5-88F1-8040-B168-F0622E113078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="600" windowWidth="21820" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -375,7 +375,7 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 81242b20-e254-4db3-9dc1-17e93fd25a4d</t>
+    <t>81242b20-e254-4db3-9dc1-17e93fd25a4d</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>

--- a/data/LINE班群提醒排程.xlsx
+++ b/data/LINE班群提醒排程.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sonialiang/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sonialiang/Desktop/兆基/LINE班群提醒排程/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A75EA5-88F1-8040-B168-F0622E113078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>

--- a/data/LINE班群提醒排程.xlsx
+++ b/data/LINE班群提醒排程.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sonialiang/Desktop/兆基/LINE班群提醒排程/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E6B7FE-4382-5C4E-83D6-3925A63F565D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7189197E-9C88-A84B-976B-A70221A3FF46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="25600" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="21460" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="提醒排程" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="63">
   <si>
     <t>提醒類別</t>
   </si>
@@ -414,6 +414,10 @@
       <t xml:space="preserve">
   ：每人上台時間為 3-5 分鐘,請控制進度</t>
     </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ua04bea4032a64049a9eabc6fe46b52c5</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -917,7 +921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1024,10 +1028,10 @@
         <v>54</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D4" s="13">
-        <v>46149</v>
+        <v>46147</v>
       </c>
       <c r="E4" s="14" t="s">
         <v>58</v>
@@ -1039,7 +1043,7 @@
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
     </row>
-    <row r="5" spans="1:9" ht="75" customHeight="1">
+    <row r="5" spans="1:9" ht="184" customHeight="1">
       <c r="A5" s="19" t="s">
         <v>56</v>
       </c>
@@ -1050,38 +1054,61 @@
         <v>55</v>
       </c>
       <c r="D5" s="13">
-        <v>46156</v>
+        <v>46149</v>
       </c>
       <c r="E5" s="14" t="s">
         <v>58</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
     </row>
-    <row r="6" spans="1:9" ht="49" customHeight="1">
-      <c r="A6" s="15" t="s">
+    <row r="6" spans="1:9" ht="75" customHeight="1">
+      <c r="A6" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="13">
+        <v>46156</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G6" s="8"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+    </row>
+    <row r="7" spans="1:9" ht="49" customHeight="1">
+      <c r="A7" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B7" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D7" s="17">
         <v>46188</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E7" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="6"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>

--- a/data/LINE班群提醒排程.xlsx
+++ b/data/LINE班群提醒排程.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sonialiang/Desktop/兆基/LINE班群提醒排程/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F101660\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7189197E-9C88-A84B-976B-A70221A3FF46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F4DDEA-B38A-471F-B269-08C4E3E6E03F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="21460" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="提醒排程" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="63">
   <si>
     <t>提醒類別</t>
   </si>
@@ -921,8 +921,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -1051,10 +1051,10 @@
         <v>54</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D5" s="13">
-        <v>46149</v>
+        <v>46148</v>
       </c>
       <c r="E5" s="14" t="s">
         <v>58</v>
@@ -1066,7 +1066,7 @@
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
     </row>
-    <row r="6" spans="1:9" ht="75" customHeight="1">
+    <row r="6" spans="1:9" ht="184" customHeight="1">
       <c r="A6" s="19" t="s">
         <v>56</v>
       </c>
@@ -1077,38 +1077,61 @@
         <v>55</v>
       </c>
       <c r="D6" s="13">
-        <v>46156</v>
+        <v>46149</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>58</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G6" s="8"/>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
     </row>
-    <row r="7" spans="1:9" ht="49" customHeight="1">
-      <c r="A7" s="15" t="s">
+    <row r="7" spans="1:9" ht="75" customHeight="1">
+      <c r="A7" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="13">
+        <v>46156</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7" s="8"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+    </row>
+    <row r="8" spans="1:9" ht="49" customHeight="1">
+      <c r="A8" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B8" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C8" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D8" s="17">
         <v>46188</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E8" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="6"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -1119,7 +1142,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
@@ -1168,7 +1191,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="70" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>

--- a/data/LINE班群提醒排程.xlsx
+++ b/data/LINE班群提醒排程.xlsx
@@ -834,8 +834,16 @@
         </is>
       </c>
       <c r="G5" s="8" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
+      <c r="H5" s="22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I5" s="22" t="inlineStr">
+        <is>
+          <t>2026/05/07 07:23</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="226" customHeight="1">
       <c r="A6" s="19" t="inlineStr">

--- a/data/LINE班群提醒排程.xlsx
+++ b/data/LINE班群提醒排程.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sonialiang/Desktop/兆基/LINE班群提醒排程/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F101660\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BB68945-6AC0-F343-8A72-DFFAAE58AF34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8AE2897-0892-4244-9734-A50FFA67541F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2600" yWindow="600" windowWidth="18200" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="提醒排程" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="79">
   <si>
     <t>提醒類別</t>
   </si>
@@ -693,235 +693,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">•  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>智慧化穿搭管理系統報告</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve">
-  ：5/16~5/19 要順稿最後修改
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
- • </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>分工合作</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>：雲渝</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>- SWOT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>分析</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>：于庭- 行銷4P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>：麗晴- 供給、價值、需求、財務</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">•  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>智慧化穿搭管理系統報告</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve">
-  ：5/13 今天要完成PPT
-  ：5/15 要開始校搞與修改
- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
- • </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>分工合作</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>：雲渝</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>- SWOT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>分析</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>：于庭- 行銷4P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>：麗晴- 供給、價值、需求、財務</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>產業創新(二) 第4小組</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -1009,7 +780,7 @@
         <family val="2"/>
         <charset val="136"/>
       </rPr>
-      <t>5/14 報告組別: 第③組→第</t>
+      <t>5/21 報告組別: 第</t>
     </r>
     <r>
       <rPr>
@@ -1017,7 +788,24 @@
         <rFont val="Segoe UI Symbol"/>
         <family val="2"/>
       </rPr>
-      <t>①</t>
+      <t>⑥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>組→第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>④</t>
     </r>
     <r>
       <rPr>
@@ -1059,6 +847,33 @@
   </si>
   <si>
     <r>
+      <t>經濟學(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>二</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>小組報告</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">• </t>
     </r>
     <r>
@@ -1068,7 +883,48 @@
         <family val="2"/>
         <charset val="136"/>
       </rPr>
-      <t>5/21 報告組別: 第</t>
+      <t>認識相關的總體經濟指標(小組報告) 
+  ：要彙整完成給群組</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">•  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>智慧化穿搭管理系統報告</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve">
+  ：5/14 今天要完成PPT (總共15頁)
+  ：5/16 要開始校搞與修改</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>5/14 報告組別: 第</t>
     </r>
     <r>
       <rPr>
@@ -1076,7 +932,7 @@
         <rFont val="Segoe UI Symbol"/>
         <family val="2"/>
       </rPr>
-      <t>⑥</t>
+      <t>③</t>
     </r>
     <r>
       <rPr>
@@ -1093,16 +949,16 @@
         <rFont val="Segoe UI Symbol"/>
         <family val="2"/>
       </rPr>
-      <t>④</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>組
+      <t>①</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>組→第⑥組→第④組
   ：今天要帶</t>
     </r>
     <r>
@@ -1135,44 +991,25 @@
   </si>
   <si>
     <r>
-      <t>經濟學(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>二</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>小組報告</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">• </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>認識相關的總體經濟指標(小組報告) 
-  ：要彙整完成給群組</t>
+      <t xml:space="preserve">•  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>智慧化穿搭管理系統報告</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve">
+  ：5/17~5/19 要順稿最後修改</t>
     </r>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -1694,7 +1531,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -1792,7 +1629,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="184" customHeight="1">
+    <row r="4" spans="1:9" ht="166.5" customHeight="1">
       <c r="A4" s="19" t="s">
         <v>55</v>
       </c>
@@ -1800,7 +1637,7 @@
         <v>53</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D4" s="13">
         <v>46149</v>
@@ -1819,7 +1656,7 @@
         <v>46149.270833333336</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="226" customHeight="1">
+    <row r="5" spans="1:9" ht="202" customHeight="1">
       <c r="A5" s="19" t="s">
         <v>55</v>
       </c>
@@ -1827,13 +1664,13 @@
         <v>61</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D5" s="13">
         <v>46148</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>62</v>
@@ -1851,27 +1688,23 @@
         <v>55</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C6" s="21" t="s">
         <v>59</v>
       </c>
       <c r="D6" s="13">
-        <v>46151</v>
+        <v>46154</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G6" s="8"/>
-      <c r="H6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="22">
-        <v>46148.270833333336</v>
-      </c>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
     </row>
     <row r="7" spans="1:9" ht="96" customHeight="1">
       <c r="A7" s="19" t="s">
@@ -1881,7 +1714,7 @@
         <v>63</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D7" s="13">
         <v>46154</v>
@@ -1890,21 +1723,21 @@
         <v>56</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G7" s="8"/>
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
     </row>
-    <row r="8" spans="1:9" ht="128" customHeight="1">
+    <row r="8" spans="1:9" ht="85.5" customHeight="1">
       <c r="A8" s="19" t="s">
         <v>55</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D8" s="13">
         <v>46155</v>
@@ -1913,7 +1746,7 @@
         <v>56</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="G8" s="8"/>
       <c r="H8" s="6"/>
@@ -1927,7 +1760,7 @@
         <v>53</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D9" s="13">
         <v>46156</v>
@@ -1936,21 +1769,21 @@
         <v>57</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G9" s="8"/>
       <c r="H9" s="6"/>
       <c r="I9" s="6"/>
     </row>
-    <row r="10" spans="1:9" ht="139" customHeight="1">
+    <row r="10" spans="1:9" ht="84.5" customHeight="1">
       <c r="A10" s="19" t="s">
         <v>55</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D10" s="13">
         <v>46158</v>
@@ -1959,7 +1792,7 @@
         <v>56</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="G10" s="8"/>
       <c r="H10" s="6"/>
@@ -1970,13 +1803,13 @@
         <v>55</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D11" s="13">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="E11" s="14" t="s">
         <v>56</v>
@@ -1996,7 +1829,7 @@
         <v>53</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D12" s="13">
         <v>46163</v>
@@ -2005,7 +1838,7 @@
         <v>57</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G12" s="8"/>
       <c r="H12" s="6"/>
@@ -2019,7 +1852,7 @@
         <v>51</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D13" s="17">
         <v>46186</v>
@@ -2041,7 +1874,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
@@ -2090,7 +1923,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="70" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>

--- a/data/LINE班群提醒排程.xlsx
+++ b/data/LINE班群提醒排程.xlsx
@@ -964,8 +964,16 @@
         </is>
       </c>
       <c r="G8" s="8" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I8" s="23" t="inlineStr">
+        <is>
+          <t>2026/05/13 08:56</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="75" customHeight="1">
       <c r="A9" s="19" t="inlineStr">

--- a/data/LINE班群提醒排程.xlsx
+++ b/data/LINE班群提醒排程.xlsx
@@ -1007,8 +1007,16 @@
         </is>
       </c>
       <c r="G9" s="8" t="n"/>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="6" t="n"/>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I9" s="23" t="inlineStr">
+        <is>
+          <t>2026/05/14 09:25</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="84.5" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
